--- a/Mapping_Rules.xlsx
+++ b/Mapping_Rules.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nhanle/Desktop/hoadonpl/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A61A49E-46C3-714A-BBC5-5F21A590FFE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E27E91C-6990-7340-B5F0-74D8208776FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="960" windowWidth="27640" windowHeight="15100" xr2:uid="{70270CC7-9655-454C-A590-78A6041B8AC8}"/>
+    <workbookView xWindow="1400" yWindow="1160" windowWidth="27640" windowHeight="15100" xr2:uid="{70270CC7-9655-454C-A590-78A6041B8AC8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="115">
   <si>
     <t>NÂNG HẠ</t>
   </si>
@@ -381,6 +381,12 @@
   </si>
   <si>
     <t>Dầu nhờn KOMAT SHD 40 - Phuy 200 lít</t>
+  </si>
+  <si>
+    <t>TKNO</t>
+  </si>
+  <si>
+    <t>TKCO</t>
   </si>
 </sst>
 </file>
@@ -767,567 +773,779 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00CB110A-EC66-0149-BE8F-9FE09842591F}">
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C2">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C3">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C4">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C5">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C6">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C7">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C8">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C9">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C10">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C11">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C12">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C13">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C14">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C15">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C16">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C17">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C18">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C19">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C20">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C21">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C22">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C23">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C24">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C25">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C26">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C27">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>65</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C28">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C29">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C30">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C31">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C32">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C33">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C34">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C35">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C36">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C37">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C38">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C39">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C40">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C41">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C42">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C43">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C44">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C45">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>75</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C46">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C47">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>78</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C48">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>80</v>
       </c>
       <c r="B49" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C49">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C50">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>82</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C51">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>84</v>
       </c>
       <c r="B52" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C52">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>86</v>
       </c>
       <c r="B53" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C53">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>88</v>
       </c>
       <c r="B54" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C54">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>90</v>
       </c>
       <c r="B55" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C55">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>92</v>
       </c>
       <c r="B56" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C56">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>94</v>
       </c>
       <c r="B57" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C57">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>95</v>
       </c>
       <c r="B58" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C58">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>98</v>
       </c>
       <c r="B59" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C59">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>99</v>
       </c>
       <c r="B60" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C60">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>100</v>
       </c>
       <c r="B61" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C61">
+        <v>1561</v>
+      </c>
+      <c r="D61">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>101</v>
       </c>
       <c r="B62" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C62">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>102</v>
       </c>
       <c r="B63" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C63">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>104</v>
       </c>
       <c r="B64" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C64">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>105</v>
       </c>
       <c r="B65" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C65">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>107</v>
       </c>
       <c r="B66" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C66">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>109</v>
       </c>
       <c r="B67" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C67">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>111</v>
       </c>
       <c r="B68" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C68">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>112</v>
       </c>
       <c r="B69" t="s">
         <v>112</v>
       </c>
+      <c r="C69">
+        <v>1562</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:B56" xr:uid="{00CB110A-EC66-0149-BE8F-9FE09842591F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Mapping_Rules.xlsx
+++ b/Mapping_Rules.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nhanle/Desktop/hoadonpl/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nhanle/Desktop/app/hoadonpl/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E27E91C-6990-7340-B5F0-74D8208776FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4F01A7-DE92-AB40-9889-FCBDA1C6CEE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="1160" windowWidth="27640" windowHeight="15100" xr2:uid="{70270CC7-9655-454C-A590-78A6041B8AC8}"/>
+    <workbookView xWindow="1160" yWindow="780" windowWidth="27640" windowHeight="15100" xr2:uid="{70270CC7-9655-454C-A590-78A6041B8AC8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="187">
   <si>
     <t>NÂNG HẠ</t>
   </si>
@@ -387,6 +387,222 @@
   </si>
   <si>
     <t>TKCO</t>
+  </si>
+  <si>
+    <t>Thu phí dịch vụ ngân hàng điện tử</t>
+  </si>
+  <si>
+    <t>Phí ngân hàng</t>
+  </si>
+  <si>
+    <t>Phí lưu kho</t>
+  </si>
+  <si>
+    <t>PHÍ LƯU CONT (DEM/DET)</t>
+  </si>
+  <si>
+    <t>Phí lưu container</t>
+  </si>
+  <si>
+    <t>PHI DICH VU NGAN HANG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu hộ KMTC phí lưu container rỗng </t>
+  </si>
+  <si>
+    <t>Thu hộ KMTC phí lưu cont rỗng (DET)</t>
+  </si>
+  <si>
+    <t>Trả lãi vay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mua Sơ Mi Rơ Moóc Tải Chở Container </t>
+  </si>
+  <si>
+    <t>RỬA HÓA CHẤT NẶNG</t>
+  </si>
+  <si>
+    <t>THU HỘ PHÍ LƯU CONTS /THUÊ CONTS (DEM CHARGE)</t>
+  </si>
+  <si>
+    <t>Thu hộ phí lưu container</t>
+  </si>
+  <si>
+    <t>DEM - JJS - Thu hộ phí lưu conts tại bãi (Demurage)</t>
+  </si>
+  <si>
+    <t>Thu hộ phí lưu container tại bãi</t>
+  </si>
+  <si>
+    <t>Bốc xếp cont 20 feet hàng từ bãi -&gt; xe</t>
+  </si>
+  <si>
+    <t>Phí bốc xếp container từ bãi đến xe</t>
+  </si>
+  <si>
+    <t>Bốc xếp cont 20 feet rỗng từ xe -&gt; bãi</t>
+  </si>
+  <si>
+    <t>Phí bốc xếp container từ xe đến bãi</t>
+  </si>
+  <si>
+    <t>Bốc xếp cont 20 feet rỗng từ xe -&gt;xe</t>
+  </si>
+  <si>
+    <t>Phí bốc xếp container từ xe đến xe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THU LAI VAY </t>
+  </si>
+  <si>
+    <t>PHÍ DỊCH VỤ CÔNG -TEN -NƠ</t>
+  </si>
+  <si>
+    <t>Phí dịch vụ container</t>
+  </si>
+  <si>
+    <t>THU HỘ PHÍ LƯU CONT TẠI CẢNG XUẤT (EX-DEM)</t>
+  </si>
+  <si>
+    <t>Thu hộ phí lưu container tại cảng xuất</t>
+  </si>
+  <si>
+    <t>Phí nhiên liệu (RON 95)</t>
+  </si>
+  <si>
+    <t>Xăng RON 95</t>
+  </si>
+  <si>
+    <t>PHỤ THU NÂNG TẠI BÃI - 40` ĐẦY</t>
+  </si>
+  <si>
+    <t>PHỤ THU NÂNG TẠI BÃI</t>
+  </si>
+  <si>
+    <t>Phụ thu phí nâng tại bãi</t>
+  </si>
+  <si>
+    <t>Cấp cont rỗng</t>
+  </si>
+  <si>
+    <t>Phí cấp container rỗng</t>
+  </si>
+  <si>
+    <t>PHI MB - CK NHANH NGOAI HE THONG NH</t>
+  </si>
+  <si>
+    <t>IB ,OTP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHỤ THU NÂNG TẠI BÃI </t>
+  </si>
+  <si>
+    <t>Ly giữ nhiệt</t>
+  </si>
+  <si>
+    <t>Cấp rỗng 20 GP</t>
+  </si>
+  <si>
+    <t>Dịch vụ tải ESIM</t>
+  </si>
+  <si>
+    <t>Cút nối ống nhôm FA-DN80</t>
+  </si>
+  <si>
+    <t>Nam châm vĩnh cửu chưa hóa từ</t>
+  </si>
+  <si>
+    <t>Đánh giá Paraffin các loại (01187/N2.25/DG)</t>
+  </si>
+  <si>
+    <t>Đánh giá Paraffin các loại</t>
+  </si>
+  <si>
+    <t>THU HỘ PHÍ LƯU CONT TẠI BÃI</t>
+  </si>
+  <si>
+    <t>Đầu dò khói AH 0311-4</t>
+  </si>
+  <si>
+    <t>Phí chuyển soi container</t>
+  </si>
+  <si>
+    <t>Chuyển soi cont hàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cước vận chuyển </t>
+  </si>
+  <si>
+    <t>Cước vận chuyển</t>
+  </si>
+  <si>
+    <t>Phí neo xe Dịch vụ vận chuyển</t>
+  </si>
+  <si>
+    <t>Phí dịch vụ phụ trội về thanh toán(FHF)</t>
+  </si>
+  <si>
+    <t>Phí dịch vụ phụ trội về thanh toán</t>
+  </si>
+  <si>
+    <t>TRẢ BÃI CONT RỖNG - 20` RỖNG</t>
+  </si>
+  <si>
+    <t>Phí trả bãi container rỗng</t>
+  </si>
+  <si>
+    <t>Phí chuyển ngang tàu, đổi cảng</t>
+  </si>
+  <si>
+    <t>Phí chuyển ngang tàu, đổi cảng chuyển tải hàng</t>
+  </si>
+  <si>
+    <t>Chuyển bãi nội bộ 40 hàng</t>
+  </si>
+  <si>
+    <t>Phí chuyển bãi nội bộ</t>
+  </si>
+  <si>
+    <t>SÀN RÁC ONEU5911747</t>
+  </si>
+  <si>
+    <t>Khác</t>
+  </si>
+  <si>
+    <t>Thanh toán tiền điện</t>
+  </si>
+  <si>
+    <t>Phụ phí chuyển cảng container hàng nhập</t>
+  </si>
+  <si>
+    <t>Phụ gia làm sạch nhiên liệu</t>
+  </si>
+  <si>
+    <t>Trả trước Gói Home</t>
+  </si>
+  <si>
+    <t>PHỤ THU NÂNG TẠI</t>
+  </si>
+  <si>
+    <t>THU DIEN PHI + PHI TT USD</t>
+  </si>
+  <si>
+    <t>Thu điện phí</t>
+  </si>
+  <si>
+    <t>CTY TNHH PHAN LONG MUA 51,284.50USD TG 26305VND/USD THANH TOAN TIEN HA NG NK TRA TRUOC CUA HD SO 0126 BM-P L FXSP.20260127.001561</t>
+  </si>
+  <si>
+    <t>Mua USD</t>
+  </si>
+  <si>
+    <t>Phí thẩm định đợt 1 hồ sơ PM.003481/26/BĐS-TD</t>
+  </si>
+  <si>
+    <t>Phí thẩm định hồ sơ</t>
+  </si>
+  <si>
+    <t>Nhãn hiệu: THACO Số loại: 3AA4012D</t>
   </si>
 </sst>
 </file>
@@ -773,7 +989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00CB110A-EC66-0149-BE8F-9FE09842591F}">
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D115"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43.5" bestFit="1" customWidth="1"/>
@@ -1297,7 +1513,7 @@
         <v>36</v>
       </c>
       <c r="C47">
-        <v>152</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -1543,6 +1759,512 @@
       </c>
       <c r="C69">
         <v>1562</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>115</v>
+      </c>
+      <c r="B70" t="s">
+        <v>116</v>
+      </c>
+      <c r="C70">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>117</v>
+      </c>
+      <c r="B71" t="s">
+        <v>117</v>
+      </c>
+      <c r="C71">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>118</v>
+      </c>
+      <c r="B72" t="s">
+        <v>119</v>
+      </c>
+      <c r="C72">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>120</v>
+      </c>
+      <c r="B73" t="s">
+        <v>116</v>
+      </c>
+      <c r="C73">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>122</v>
+      </c>
+      <c r="B74" t="s">
+        <v>121</v>
+      </c>
+      <c r="C74">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>186</v>
+      </c>
+      <c r="B75" t="s">
+        <v>124</v>
+      </c>
+      <c r="C75">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>125</v>
+      </c>
+      <c r="B76" t="s">
+        <v>18</v>
+      </c>
+      <c r="C76">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>126</v>
+      </c>
+      <c r="B77" t="s">
+        <v>127</v>
+      </c>
+      <c r="C77">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>128</v>
+      </c>
+      <c r="B78" t="s">
+        <v>129</v>
+      </c>
+      <c r="C78">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>130</v>
+      </c>
+      <c r="B79" t="s">
+        <v>131</v>
+      </c>
+      <c r="C79">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>132</v>
+      </c>
+      <c r="B80" t="s">
+        <v>133</v>
+      </c>
+      <c r="C80">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>134</v>
+      </c>
+      <c r="B81" t="s">
+        <v>135</v>
+      </c>
+      <c r="C81">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>136</v>
+      </c>
+      <c r="B82" t="s">
+        <v>123</v>
+      </c>
+      <c r="C82">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>137</v>
+      </c>
+      <c r="B83" t="s">
+        <v>138</v>
+      </c>
+      <c r="C83">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>139</v>
+      </c>
+      <c r="B84" t="s">
+        <v>140</v>
+      </c>
+      <c r="C84">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>142</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C85">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>144</v>
+      </c>
+      <c r="B86" t="s">
+        <v>145</v>
+      </c>
+      <c r="C86">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>146</v>
+      </c>
+      <c r="B87" t="s">
+        <v>147</v>
+      </c>
+      <c r="C87">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>148</v>
+      </c>
+      <c r="B88" t="s">
+        <v>116</v>
+      </c>
+      <c r="C88">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>149</v>
+      </c>
+      <c r="B89" t="s">
+        <v>116</v>
+      </c>
+      <c r="C89">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>150</v>
+      </c>
+      <c r="B90" t="s">
+        <v>145</v>
+      </c>
+      <c r="C90">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>143</v>
+      </c>
+      <c r="B91" t="s">
+        <v>145</v>
+      </c>
+      <c r="C91">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>151</v>
+      </c>
+      <c r="B92" t="s">
+        <v>151</v>
+      </c>
+      <c r="C92">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>152</v>
+      </c>
+      <c r="B93" t="s">
+        <v>147</v>
+      </c>
+      <c r="C93">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>153</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C94">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>154</v>
+      </c>
+      <c r="B95" t="s">
+        <v>154</v>
+      </c>
+      <c r="C95">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>155</v>
+      </c>
+      <c r="B96" t="s">
+        <v>155</v>
+      </c>
+      <c r="C96">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>156</v>
+      </c>
+      <c r="B97" t="s">
+        <v>157</v>
+      </c>
+      <c r="C97">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>158</v>
+      </c>
+      <c r="B98" t="s">
+        <v>129</v>
+      </c>
+      <c r="C98">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>159</v>
+      </c>
+      <c r="B99" t="s">
+        <v>159</v>
+      </c>
+      <c r="C99">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>161</v>
+      </c>
+      <c r="B100" t="s">
+        <v>160</v>
+      </c>
+      <c r="C100">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>162</v>
+      </c>
+      <c r="B101" t="s">
+        <v>163</v>
+      </c>
+      <c r="C101">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>164</v>
+      </c>
+      <c r="B102" t="s">
+        <v>164</v>
+      </c>
+      <c r="C102">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>165</v>
+      </c>
+      <c r="B103" t="s">
+        <v>166</v>
+      </c>
+      <c r="C103">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>167</v>
+      </c>
+      <c r="B104" t="s">
+        <v>168</v>
+      </c>
+      <c r="C104">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>169</v>
+      </c>
+      <c r="B105" t="s">
+        <v>170</v>
+      </c>
+      <c r="C105">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>171</v>
+      </c>
+      <c r="B106" t="s">
+        <v>172</v>
+      </c>
+      <c r="C106">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>173</v>
+      </c>
+      <c r="B107" t="s">
+        <v>18</v>
+      </c>
+      <c r="C107">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>174</v>
+      </c>
+      <c r="B108" t="s">
+        <v>175</v>
+      </c>
+      <c r="C108">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>176</v>
+      </c>
+      <c r="B109" t="s">
+        <v>176</v>
+      </c>
+      <c r="C109">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>177</v>
+      </c>
+      <c r="B110" t="s">
+        <v>177</v>
+      </c>
+      <c r="C110">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>178</v>
+      </c>
+      <c r="B111" t="s">
+        <v>178</v>
+      </c>
+      <c r="C111">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>179</v>
+      </c>
+      <c r="B112" t="s">
+        <v>145</v>
+      </c>
+      <c r="C112">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>180</v>
+      </c>
+      <c r="B113" t="s">
+        <v>181</v>
+      </c>
+      <c r="C113">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>182</v>
+      </c>
+      <c r="B114" t="s">
+        <v>183</v>
+      </c>
+      <c r="C114">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>184</v>
+      </c>
+      <c r="B115" t="s">
+        <v>185</v>
+      </c>
+      <c r="C115">
+        <v>6427</v>
       </c>
     </row>
   </sheetData>
